--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>GTLB</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>149700</v>
+      </c>
+      <c r="E8" s="3">
         <v>139600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>126900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>122900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>113000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>101000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>87400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>77800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>66800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>58100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>46100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29500</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E9" s="3">
         <v>14700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>7200</v>
       </c>
       <c r="L9" s="3">
         <v>7200</v>
       </c>
       <c r="M9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="N9" s="3">
         <v>6400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4600</v>
-      </c>
-      <c r="P9" s="3">
-        <v>3800</v>
       </c>
       <c r="Q9" s="3">
         <v>3800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
+      <c r="R9" s="3">
+        <v>3800</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E10" s="3">
         <v>125000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>113400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>108700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>98400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>88000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>77600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>68600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>59600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>50900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>43500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>39900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>37600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>30600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25700</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -928,52 +942,55 @@
         <v>49000</v>
       </c>
       <c r="E12" s="3">
+        <v>49000</v>
+      </c>
+      <c r="F12" s="3">
         <v>48300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>43700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>41100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>39500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>31800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>28600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>21300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>48700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19100</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,20 +1042,23 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7700</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1046,11 +1066,11 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-17800</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1066,8 +1086,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1078,8 +1098,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E17" s="3">
         <v>193600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>185100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>169200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>169900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>166300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>112500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>118400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>99300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>88000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>76000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>174600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>66600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>63300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>61600</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-54000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-58200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-46300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-56900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-65300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-25100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-40600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-29900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-128500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-32100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,91 +1309,95 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6800</v>
+        <v>10700</v>
       </c>
       <c r="E20" s="3">
         <v>6800</v>
       </c>
       <c r="F20" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G20" s="3">
         <v>4500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>20000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1700</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-45500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-49700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-40100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-48900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-60200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-23000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-48700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-42500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1370,20 +1407,23 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1435,114 +1475,123 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-47200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-51400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-41700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-50400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-61600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-42600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-39800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-118400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-33800</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>256800</v>
+      </c>
+      <c r="E24" s="3">
         <v>4000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-286400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-51200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-52900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-42100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-50500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-61500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-46800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-41700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-40800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-120000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34200</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-285200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-50100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-52500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-48500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-59000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-45800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-40200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-120000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34200</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6800</v>
+        <v>-10700</v>
       </c>
       <c r="E32" s="3">
         <v>-6800</v>
       </c>
       <c r="F32" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="G32" s="3">
         <v>-4500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1700</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-285200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-50100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-52500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-48500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-59000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-45800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-40200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-120000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34200</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-285200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-50100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-52500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-48500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-59000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-45800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-40200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-120000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34200</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,41 +2310,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>285300</v>
+      </c>
+      <c r="E41" s="3">
         <v>273200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>315900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>295400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>372200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>410800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>887500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>884700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>824700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>276300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2277,38 +2364,41 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>704300</v>
+      </c>
+      <c r="E42" s="3">
         <v>713100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>621700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>641200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>555600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>519400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>47300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>50000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100000</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2324,47 +2414,50 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>135600</v>
+      </c>
+      <c r="E43" s="3">
         <v>105800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>131100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>101500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>93000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>71300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>80400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>57000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46900</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2383,8 +2476,11 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2436,41 +2532,44 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E45" s="3">
         <v>51100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>49900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>50200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>40200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>40800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>36700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27500</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,41 +2588,44 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1182300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1143200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1115200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1118000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1069400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1064000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1044200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1051800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1012400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>350700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,32 +2644,35 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E47" s="3">
         <v>10600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15600</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2583,8 +2688,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2595,35 +2700,38 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2639,8 +2747,8 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -2648,41 +2756,44 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E49" s="3">
         <v>10900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,41 +2924,44 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E52" s="3">
         <v>19600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,41 +3036,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1226900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1189100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1164100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1169200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1120200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1115400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1099000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1091400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1028800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>366400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,8 +3092,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,41 +3138,42 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,8 +3192,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3081,12 +3215,12 @@
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>2900</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3102,8 +3236,8 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3114,41 +3248,44 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>580900</v>
+      </c>
+      <c r="E59" s="3">
         <v>317000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>308000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>301100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>258200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>241300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>226000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>236600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>173900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>149500</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,41 +3304,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>585900</v>
+      </c>
+      <c r="E60" s="3">
         <v>321200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>311100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>306300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>264500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>246700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>234600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>241600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>178900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>151500</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3220,8 +3360,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3273,40 +3416,43 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E62" s="3">
         <v>36600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>37500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>41100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>46200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>50600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>40500</v>
       </c>
       <c r="L62" s="3">
         <v>40500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>40500</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,41 +3640,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>680300</v>
+      </c>
+      <c r="E66" s="3">
         <v>405400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>398600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>398200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>356700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>336900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>316900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>316600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>244400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>217500</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3538,8 +3696,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3695,11 +3863,11 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>424900</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,41 +3942,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1113400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-828200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-778100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-725600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-686900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-638500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-579400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-553300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-507600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-466300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3824,8 +3998,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,41 +4166,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>546600</v>
+      </c>
+      <c r="E76" s="3">
         <v>783700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>765500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>771000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>763600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>778500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>782100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>774900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>784400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-276000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4036,8 +4222,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-285200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-50100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-52500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-48500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-59000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-45800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-40200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-120000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34200</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,38 +4419,39 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E83" s="3">
         <v>1700</v>
       </c>
       <c r="F83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4268,14 +4467,17 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,38 +4753,41 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E89" s="3">
         <v>27100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-36300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10100</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4586,14 +4803,17 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,40 +4833,41 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-700</v>
       </c>
       <c r="E91" s="3">
         <v>-300</v>
       </c>
       <c r="F91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -4654,8 +4875,8 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,38 +4999,41 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-89400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-81800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-474700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>46100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4819,14 +5049,17 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,38 +5301,41 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E100" s="3">
         <v>18000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>34800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>43700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>658900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5105,44 +5351,47 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5158,44 +5407,47 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-45200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-76800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-38600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-476700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>62500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>548500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5211,10 +5463,13 @@
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>GTLB</t>
   </si>
@@ -656,263 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>169200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>163800</v>
+      </c>
+      <c r="F8" s="3">
         <v>149700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>139600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>126900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>122900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>113000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>101000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>87400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>77800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>66800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>58100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>49900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>46100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>42200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>34400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>29500</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F9" s="3">
         <v>15100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>14700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>13500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>14200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>14600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>13000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>9800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>9200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>7200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>7200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>6400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>4600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>150400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>147800</v>
+      </c>
+      <c r="F10" s="3">
         <v>134600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>125000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>113400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>108700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>98400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>88000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>77600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>68600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>59600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>50900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>43500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>39900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>37600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>30600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>25700</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +958,72 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>52400</v>
+      </c>
+      <c r="F12" s="3">
         <v>49000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>49000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>48300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>43700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>41100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>39500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>31800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>28600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>24700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>22600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>21300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>48700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>19000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>19800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>19100</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,38 +1078,44 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E14" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>7700</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-17800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1089,11 +1128,11 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1101,8 +1140,14 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1202,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1227,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>222800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>207500</v>
+      </c>
+      <c r="F17" s="3">
         <v>189900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>193600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>185100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>169200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>169900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>166300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>112500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>118400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>99300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>88000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>76000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>174600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>66600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>63300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>61600</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-40200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-54000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-58200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-46300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-56900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-65300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-25100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-40600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-32500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-29900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-26100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-128500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-28900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-32100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,120 +1375,134 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F20" s="3">
         <v>10700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>6800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>6800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>6500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-9100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-10100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-9900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>10100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>20000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-1700</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-27900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-45500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-49700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-40100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-48900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-60200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-23000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-48700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-42500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-8800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1478,120 +1557,138 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-29600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-47200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-51400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-41700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-50400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-61600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-24100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-49600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-42600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-39800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-27000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-118400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-8800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-33800</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F24" s="3">
         <v>256800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1743,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-286400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-51200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-52900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-42100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-50500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-61500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-26600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-46800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-41700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-40800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-28300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-120000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-9400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-34200</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-285200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-50100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-52500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-38700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-48500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-59000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-26100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-45800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-41200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-40200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-27900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-120000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-9400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-34200</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2115,138 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-10700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-6800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-6800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-6500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>9100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>10100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>9900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-10100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-20000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>1700</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-285200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-50100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-52500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-38700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-48500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-59000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-26100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-45800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-41200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-40200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-27900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-120000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-9400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-34200</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2301,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-285200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-50100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-52500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-38700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-48500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-59000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-26100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-45800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-41200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-40200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-27900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-120000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-9400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-34200</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,47 +2482,49 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>420300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>288000</v>
+      </c>
+      <c r="F41" s="3">
         <v>285300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>273200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>315900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>295400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>372200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>410800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>887500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>884700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>824700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>276300</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,44 +2540,50 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>641200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>748300</v>
+      </c>
+      <c r="F42" s="3">
         <v>704300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>713100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>621700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>641200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>555600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>519400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>47300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>50000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>100000</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2417,53 +2596,59 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>170900</v>
+      </c>
+      <c r="F43" s="3">
         <v>135600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>105800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>127700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>131100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>101500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>93000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>71300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>80400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>57000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>46900</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2479,8 +2664,14 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,47 +2726,53 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>66400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>73700</v>
+      </c>
+      <c r="F45" s="3">
         <v>57100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>51100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>49900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>50200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>40200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>40800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>38100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>36700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>30600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>27500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,47 +2788,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1263000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1280900</v>
+      </c>
+      <c r="F46" s="3">
         <v>1182300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1143200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1115200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1118000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1069400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1064000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1044200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1051800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1012400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>350700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,38 +2850,44 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
         <v>9600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>10600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>11700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>12700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>13600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>14600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>15600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,11 +2900,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2703,41 +2912,47 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F48" s="3">
         <v>4200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,56 +2965,62 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F49" s="3">
         <v>10400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>10900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>11500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>12000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>12600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>13200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>13800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>14400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +3036,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,47 +3160,53 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F52" s="3">
         <v>20300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>19600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>19500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>19700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>19000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>18200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>20900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>21900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>15900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>15100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2983,8 +3222,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,47 +3284,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1321600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1317900</v>
+      </c>
+      <c r="F54" s="3">
         <v>1226900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1189100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1164100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1169200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1120200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1115400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1099000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1091400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1028800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>366400</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3346,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,47 +3398,49 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F57" s="3">
         <v>5000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>5200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3195,38 +3456,44 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>2900</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3239,11 +3506,11 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3251,47 +3518,53 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>671300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>660300</v>
+      </c>
+      <c r="F59" s="3">
         <v>580900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>317000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>308000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>301100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>258200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>241300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>226000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>236600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>173900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>149500</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,47 +3580,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>674500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>662100</v>
+      </c>
+      <c r="F60" s="3">
         <v>585900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>321200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>311100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>306300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>264500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>246700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>234600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>241600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>178900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>151500</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,8 +3642,14 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3419,47 +3704,53 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>37900</v>
+      </c>
+      <c r="F62" s="3">
         <v>47800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>36600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>37500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>38200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>41100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>38400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>46200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>50600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>40500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>40500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3766,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,47 +3952,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>753800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>746700</v>
+      </c>
+      <c r="F66" s="3">
         <v>680300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>405400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>398600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>398200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>356700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>336900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>316900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>316600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>244400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>217500</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3699,8 +4014,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +4162,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3866,14 +4201,14 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>424900</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3889,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,47 +4286,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1204500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1149800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1113400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-828200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-778100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-725600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-686900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-638500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-579400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-553300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-507600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-466300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4348,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,47 +4534,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>567800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>571200</v>
+      </c>
+      <c r="F76" s="3">
         <v>546600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>783700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>765500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>771000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>763600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>778500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>782100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>774900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>784400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-276000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4225,8 +4596,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4658,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-285200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-50100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-52500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-38700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-48500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-59000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-26100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-45800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-41200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-40200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-27900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-120000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-9400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-34200</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,44 +4815,46 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G83" s="3">
         <v>1700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4470,14 +4867,20 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,44 +5183,50 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-6000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>27100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-11000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-11700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-36300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-28200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-10100</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4806,14 +5239,20 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5273,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4846,43 +5287,43 @@
         <v>-300</v>
       </c>
       <c r="F91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -4890,8 +5331,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,44 +5455,50 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>89400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="F94" s="3">
         <v>14600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-89400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>24400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-81800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-40400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-474700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-8800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>46100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-100000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5052,14 +5511,20 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5545,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5603,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,44 +5789,50 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F100" s="3">
         <v>4700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>18000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>7500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>11900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>7100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>34800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>43700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>9600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>658900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5354,50 +5845,56 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>4900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-3900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>7800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5410,50 +5907,56 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>132300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F102" s="3">
         <v>12100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-45200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>20500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-76800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-38600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-476700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>62500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>548500</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,10 +5969,16 @@
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDCA305-7727-49C0-B983-33A812980FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9345"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GTLB" sheetId="6" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>GTLB</t>
   </si>
@@ -303,7 +304,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -369,9 +370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -409,9 +410,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -446,7 +447,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,7 +482,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,9 +655,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -675,21 +676,20 @@
     <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -744,14 +744,8 @@
       <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -806,14 +800,8 @@
       <c r="T8" s="3">
         <v>29500</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -868,14 +856,8 @@
       <c r="T9" s="3">
         <v>3800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -930,14 +912,8 @@
       <c r="T10" s="3">
         <v>25700</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,10 +934,8 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1016,14 +990,8 @@
       <c r="T12" s="3">
         <v>19100</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1078,14 +1046,8 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-      <c r="U13" s="3">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1140,14 +1102,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1202,14 +1158,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1227,10 +1177,8 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1285,14 +1233,8 @@
       <c r="T17" s="3">
         <v>61600</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1347,14 +1289,8 @@
       <c r="T18" s="3">
         <v>-32100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,10 +1311,8 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1433,14 +1367,8 @@
       <c r="T20" s="3">
         <v>-1700</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1495,14 +1423,8 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1557,14 +1479,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1619,14 +1535,8 @@
       <c r="T23" s="3">
         <v>-33800</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1681,14 +1591,8 @@
       <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1743,14 +1647,8 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-      <c r="U25" s="3">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1805,14 +1703,8 @@
       <c r="T26" s="3">
         <v>-34200</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1867,14 +1759,8 @@
       <c r="T27" s="3">
         <v>-34200</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1929,14 +1815,8 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-      <c r="U28" s="3">
-        <v>0</v>
-      </c>
-      <c r="V28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1991,14 +1871,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2053,14 +1927,8 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-      <c r="U30" s="3">
-        <v>0</v>
-      </c>
-      <c r="V30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2115,14 +1983,8 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-      <c r="U31" s="3">
-        <v>0</v>
-      </c>
-      <c r="V31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2177,14 +2039,8 @@
       <c r="T32" s="3">
         <v>1700</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2239,14 +2095,8 @@
       <c r="T33" s="3">
         <v>-34200</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2301,14 +2151,8 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-      <c r="U34" s="3">
-        <v>0</v>
-      </c>
-      <c r="V34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2363,19 +2207,13 @@
       <c r="T35" s="3">
         <v>-34200</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
@@ -2430,14 +2268,8 @@
       <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2458,10 +2290,8 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2482,10 +2312,8 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2540,14 +2368,8 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2602,14 +2424,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2664,14 +2480,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2726,14 +2536,8 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2788,14 +2592,8 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2850,14 +2648,8 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2912,14 +2704,8 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2974,14 +2760,8 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3036,14 +2816,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3098,14 +2872,8 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-      <c r="U50" s="3">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3160,14 +2928,8 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-      <c r="U51" s="3">
-        <v>0</v>
-      </c>
-      <c r="V51" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3222,14 +2984,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3284,14 +3040,8 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-      <c r="U53" s="3">
-        <v>0</v>
-      </c>
-      <c r="V53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3346,14 +3096,8 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3374,10 +3118,8 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3398,10 +3140,8 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3456,14 +3196,8 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3518,14 +3252,8 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3580,14 +3308,8 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3642,14 +3364,8 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3704,14 +3420,8 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3766,14 +3476,8 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3828,14 +3532,8 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-      <c r="U63" s="3">
-        <v>0</v>
-      </c>
-      <c r="V63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3890,14 +3588,8 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-      <c r="U64" s="3">
-        <v>0</v>
-      </c>
-      <c r="V64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3952,14 +3644,8 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-      <c r="U65" s="3">
-        <v>0</v>
-      </c>
-      <c r="V65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4014,14 +3700,8 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4042,10 +3722,8 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4100,14 +3778,8 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-      <c r="U68" s="3">
-        <v>0</v>
-      </c>
-      <c r="V68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4162,14 +3834,8 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-      <c r="U69" s="3">
-        <v>0</v>
-      </c>
-      <c r="V69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4224,14 +3890,8 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4286,14 +3946,8 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-      <c r="U71" s="3">
-        <v>0</v>
-      </c>
-      <c r="V71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4348,14 +4002,8 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4410,14 +4058,8 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-      <c r="U73" s="3">
-        <v>0</v>
-      </c>
-      <c r="V73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4472,14 +4114,8 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-      <c r="U74" s="3">
-        <v>0</v>
-      </c>
-      <c r="V74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4534,14 +4170,8 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-      <c r="U75" s="3">
-        <v>0</v>
-      </c>
-      <c r="V75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4596,14 +4226,8 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4658,19 +4282,13 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-      <c r="U77" s="3">
-        <v>0</v>
-      </c>
-      <c r="V77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
@@ -4725,14 +4343,8 @@
       <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4787,14 +4399,8 @@
       <c r="T81" s="3">
         <v>-34200</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4815,10 +4421,8 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4873,14 +4477,8 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4935,14 +4533,8 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-      <c r="U84" s="3">
-        <v>0</v>
-      </c>
-      <c r="V84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4997,14 +4589,8 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-      <c r="U85" s="3">
-        <v>0</v>
-      </c>
-      <c r="V85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5059,14 +4645,8 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-      <c r="U86" s="3">
-        <v>0</v>
-      </c>
-      <c r="V86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5121,14 +4701,8 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-      <c r="U87" s="3">
-        <v>0</v>
-      </c>
-      <c r="V87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5183,14 +4757,8 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-      <c r="U88" s="3">
-        <v>0</v>
-      </c>
-      <c r="V88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5245,14 +4813,8 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5273,10 +4835,8 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5331,14 +4891,8 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5393,14 +4947,8 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-      <c r="U92" s="3">
-        <v>0</v>
-      </c>
-      <c r="V92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5455,14 +5003,8 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-      <c r="U93" s="3">
-        <v>0</v>
-      </c>
-      <c r="V93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5517,14 +5059,8 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5545,10 +5081,8 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5603,14 +5137,8 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5665,14 +5193,8 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-      <c r="U97" s="3">
-        <v>0</v>
-      </c>
-      <c r="V97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5727,14 +5249,8 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-      <c r="U98" s="3">
-        <v>0</v>
-      </c>
-      <c r="V98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5789,14 +5305,8 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-      <c r="U99" s="3">
-        <v>0</v>
-      </c>
-      <c r="V99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5851,14 +5361,8 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5913,14 +5417,8 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5974,12 +5472,6 @@
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDCA305-7727-49C0-B983-33A812980FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="GTLB" sheetId="6" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
   <si>
     <t>GTLB</t>
   </si>
@@ -304,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -370,9 +369,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -410,9 +409,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,7 +446,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -482,7 +481,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -655,265 +654,278 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>182600</v>
+      </c>
+      <c r="E8" s="3">
         <v>169200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>163800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>149700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>139600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>126900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>122900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>113000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>101000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>87400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>77800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>66800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>58100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>42200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E9" s="3">
         <v>18800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9200</v>
-      </c>
-      <c r="N9" s="3">
-        <v>7200</v>
       </c>
       <c r="O9" s="3">
         <v>7200</v>
       </c>
       <c r="P9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Q9" s="3">
         <v>6400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4600</v>
-      </c>
-      <c r="S9" s="3">
-        <v>3800</v>
       </c>
       <c r="T9" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>161200</v>
+      </c>
+      <c r="E10" s="3">
         <v>150400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>147800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>134600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>125000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>113400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>108700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>98400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>77600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>68600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>59600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>50900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>43500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>39900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>30600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E12" s="3">
         <v>54100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52400</v>
-      </c>
-      <c r="F12" s="3">
-        <v>49000</v>
       </c>
       <c r="G12" s="3">
         <v>49000</v>
       </c>
       <c r="H12" s="3">
+        <v>49000</v>
+      </c>
+      <c r="I12" s="3">
         <v>48300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>43700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>41100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>39500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>31800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>48700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,29 +1062,32 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>9000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7700</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
@@ -1076,11 +1095,11 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-17800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1096,14 +1115,17 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1158,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>223600</v>
+      </c>
+      <c r="E17" s="3">
         <v>222800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>207500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>189900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>193600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>185100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>169200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>169900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>166300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>112500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>118400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>99300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>88000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>76000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>174600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>66600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>63300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>61600</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-53600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-40200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-54000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-58200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-46300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-56900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-65300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-25100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-40600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-29900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-128500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-24400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-28900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,103 +1343,107 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E20" s="3">
         <v>11500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>6800</v>
       </c>
       <c r="H20" s="3">
         <v>6800</v>
       </c>
       <c r="I20" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J20" s="3">
         <v>4500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>20000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-40200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-34200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-27900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-45500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-49700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-40100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-48900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-60200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-23000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-48700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-42500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,14 +1453,17 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-8800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1479,120 +1518,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-42200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-47200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-51400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-50400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-61600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-49600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-42600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-39800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-118400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-33800</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E24" s="3">
         <v>12700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>256800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-37600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-286400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-51200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-52900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-42100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-50500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-61500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-46800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-41700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-40800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-120000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-28600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-54600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-36500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-285200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-50100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-52500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-48500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-59000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-45800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-41200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-40200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-120000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-28600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-6800</v>
       </c>
       <c r="H32" s="3">
         <v>-6800</v>
       </c>
       <c r="I32" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-20000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-54600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-36500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-285200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-50100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-52500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-48500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-59000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-45800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-41200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-40200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-120000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-28600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-54600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-36500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-285200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-50100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-52500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-48500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-59000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-45800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-41200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-40200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-120000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-28600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,50 +2397,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>438600</v>
+      </c>
+      <c r="E41" s="3">
         <v>420300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>288000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>285300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>273200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>315900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>295400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>372200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>410800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>887500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>884700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>824700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>276300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,47 +2454,50 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>644500</v>
+      </c>
+      <c r="E42" s="3">
         <v>641200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>748300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>704300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>713100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>621700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>641200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>555600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>519400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>47300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>50000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>100000</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,50 +2513,53 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E43" s="3">
         <v>135200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>170900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>105800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>131100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>93000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>71300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>80400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>57000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46900</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2480,8 +2572,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2536,50 +2631,53 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E45" s="3">
         <v>66400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>73700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>57100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>51100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>49900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>50200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>40200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27500</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2592,50 +2690,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1314400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1263000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1280900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1182300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1143200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1115200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1118000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1069400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1064000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1044200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1051800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1012400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>350700</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,41 +2749,44 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
         <v>9600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15600</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2698,14 +2802,17 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2716,32 +2823,32 @@
         <v>3400</v>
       </c>
       <c r="F48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G48" s="3">
         <v>4200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2757,53 +2864,56 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E49" s="3">
         <v>32700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>600</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,50 +3044,53 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E52" s="3">
         <v>22500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2984,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,50 +3162,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1376300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1321600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1317900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1226900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1189100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1164100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1169200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1120200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1115400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1099000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1091400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1028800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>366400</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,8 +3269,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3149,41 +3279,41 @@
         <v>3200</v>
       </c>
       <c r="E57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,8 +3326,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3222,15 +3355,15 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>2900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3246,56 +3379,59 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>663600</v>
+      </c>
+      <c r="E59" s="3">
         <v>671300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>660300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>580900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>317000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>308000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>301100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>258200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>241300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>226000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>236600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>173900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>149500</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,50 +3444,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>666800</v>
+      </c>
+      <c r="E60" s="3">
         <v>674500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>662100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>585900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>321200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>311100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>306300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>264500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>246700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>234600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>241600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>178900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>151500</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3364,8 +3503,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3420,49 +3562,52 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E62" s="3">
         <v>32700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>37900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>47800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>36600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>37500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>41100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>46200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>50600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>40500</v>
       </c>
       <c r="O62" s="3">
         <v>40500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>40500</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3476,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,50 +3798,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>733400</v>
+      </c>
+      <c r="E66" s="3">
         <v>753800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>746700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>680300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>405400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>398600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>398200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>356700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>336900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>316900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>316600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>244400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>217500</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3700,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3873,11 +4040,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>424900</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,50 +4116,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1191500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1204500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1149800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1113400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-828200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-778100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-725600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-686900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-638500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-579400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-553300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-507600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-466300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4002,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,50 +4352,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>642800</v>
+      </c>
+      <c r="E76" s="3">
         <v>567800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>571200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>546600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>783700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>765500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>771000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>763600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>778500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>782100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>774900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>784400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-276000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4226,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-54600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-36500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-285200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-50100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-52500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-48500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-59000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-45800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-41200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-40200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-120000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-28600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,47 +4618,48 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1600</v>
       </c>
       <c r="F83" s="3">
         <v>1600</v>
       </c>
       <c r="G83" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="H83" s="3">
         <v>1700</v>
       </c>
       <c r="I83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4477,8 +4675,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,47 +4970,50 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E89" s="3">
         <v>38100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-36300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10100</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4813,8 +5029,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,49 +5054,50 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-300</v>
       </c>
       <c r="H91" s="3">
         <v>-300</v>
       </c>
       <c r="I91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4885,14 +5105,17 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,47 +5229,50 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E94" s="3">
         <v>89400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>14600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-89400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>24400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-81800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-40400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-474700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>46100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5059,8 +5288,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5137,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,47 +5547,50 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E100" s="3">
         <v>5100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>18000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>11900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>34800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>43700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>658900</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5361,47 +5606,50 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5417,47 +5665,50 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E102" s="3">
         <v>132300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-45200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-76800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-476700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>62500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>548500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5471,6 +5722,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>GTLB</t>
   </si>
@@ -656,276 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E8" s="3">
         <v>182600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>169200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>163800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>149700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>139600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>126900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>122900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>113000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>101000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>87400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>77800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>66800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>58100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>49900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>42200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E9" s="3">
         <v>21400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9200</v>
-      </c>
-      <c r="O9" s="3">
-        <v>7200</v>
       </c>
       <c r="P9" s="3">
         <v>7200</v>
       </c>
       <c r="Q9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="R9" s="3">
         <v>6400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4600</v>
-      </c>
-      <c r="T9" s="3">
-        <v>3800</v>
       </c>
       <c r="U9" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>173900</v>
+      </c>
+      <c r="E10" s="3">
         <v>161200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>150400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>147800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>134600</v>
       </c>
-      <c r="H10" s="3">
-        <v>125000</v>
-      </c>
       <c r="I10" s="3">
+        <v>124900</v>
+      </c>
+      <c r="J10" s="3">
         <v>113400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>108700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>98400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>68600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>59600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>50900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>43500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>39900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>37600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>30600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,67 +960,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E12" s="3">
         <v>60900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>54100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>52400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>49000</v>
       </c>
       <c r="H12" s="3">
         <v>49000</v>
       </c>
       <c r="I12" s="3">
+        <v>49000</v>
+      </c>
+      <c r="J12" s="3">
         <v>48300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>43700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>41100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>39500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>21300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>48700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,32 +1082,35 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
-        <v>1000</v>
-      </c>
       <c r="F14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G14" s="3">
         <v>9000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7700</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1098,11 +1118,11 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-17800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1118,37 +1138,40 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,8 +1229,9 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1215,114 +1242,120 @@
         <v>222800</v>
       </c>
       <c r="F17" s="3">
-        <v>207500</v>
+        <v>220500</v>
       </c>
       <c r="G17" s="3">
+        <v>198500</v>
+      </c>
+      <c r="H17" s="3">
         <v>189900</v>
       </c>
-      <c r="H17" s="3">
-        <v>193600</v>
-      </c>
       <c r="I17" s="3">
-        <v>185100</v>
+        <v>193500</v>
       </c>
       <c r="J17" s="3">
+        <v>177500</v>
+      </c>
+      <c r="K17" s="3">
         <v>169200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>169900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>166300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>112500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>118400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>99300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>88000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>76000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>174600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>66600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>63300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>61600</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-41000</v>
+        <v>-27600</v>
       </c>
       <c r="E18" s="3">
-        <v>-53600</v>
+        <v>-40200</v>
       </c>
       <c r="F18" s="3">
-        <v>-43700</v>
+        <v>-51300</v>
       </c>
       <c r="G18" s="3">
-        <v>-40200</v>
+        <v>-34700</v>
       </c>
       <c r="H18" s="3">
-        <v>-54000</v>
+        <v>-40300</v>
       </c>
       <c r="I18" s="3">
-        <v>-58200</v>
+        <v>-53900</v>
       </c>
       <c r="J18" s="3">
+        <v>-50600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-46300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-56900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-65300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-25100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-40600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-32500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-29900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-26100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-128500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-24400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-28900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,109 +1377,113 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>13800</v>
+        <v>-5000</v>
       </c>
       <c r="E20" s="3">
-        <v>11500</v>
+        <v>-1000</v>
       </c>
       <c r="F20" s="3">
-        <v>7900</v>
+        <v>600</v>
       </c>
       <c r="G20" s="3">
-        <v>10700</v>
+        <v>3900</v>
       </c>
       <c r="H20" s="3">
-        <v>6800</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>6800</v>
+        <v>2200</v>
       </c>
       <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
         <v>4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>20000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-24100</v>
+        <v>-19400</v>
       </c>
       <c r="E21" s="3">
-        <v>-40200</v>
+        <v>-38400</v>
       </c>
       <c r="F21" s="3">
-        <v>-34200</v>
+        <v>-51000</v>
       </c>
       <c r="G21" s="3">
-        <v>-27900</v>
+        <v>-37600</v>
       </c>
       <c r="H21" s="3">
-        <v>-45500</v>
+        <v>-39300</v>
       </c>
       <c r="I21" s="3">
-        <v>-49700</v>
+        <v>-55000</v>
       </c>
       <c r="J21" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-40100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-48900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-60200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-23000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-48700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-42500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1456,37 +1493,40 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-8800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1521,67 +1561,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-42200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-47200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-51400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-50400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-61600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-49600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-42600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-118400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-28400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-33800</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1589,58 +1635,61 @@
         <v>-39400</v>
       </c>
       <c r="E24" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="F24" s="3">
         <v>12700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>256800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E26" s="3">
         <v>12300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-54900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-37600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-286400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-51200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-52900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-42100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-50500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-61500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-46800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-41700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-28300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-120000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-28600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E27" s="3">
         <v>12900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-54600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-36500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-285200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-50100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-52500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-48500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-59000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-45800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-41200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-27900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-120000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-28600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-13800</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="3">
-        <v>-11500</v>
+        <v>1000</v>
       </c>
       <c r="F32" s="3">
-        <v>-7900</v>
+        <v>-600</v>
       </c>
       <c r="G32" s="3">
-        <v>-10700</v>
+        <v>-3900</v>
       </c>
       <c r="H32" s="3">
-        <v>-6800</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>-6800</v>
+        <v>-2200</v>
       </c>
       <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-20000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E33" s="3">
         <v>12900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-54600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-36500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-285200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-50100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-52500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-48500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-59000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-45800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-41200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-27900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-120000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-28600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E35" s="3">
         <v>12900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-54600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-36500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-285200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-50100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-52500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-48500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-59000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-45800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-41200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-27900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-120000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-28600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,53 +2484,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>176600</v>
+      </c>
+      <c r="E41" s="3">
         <v>438600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>420300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>288000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>285300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>273200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>315900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>295400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>372200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>410800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>887500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>884700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>824700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>276300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,50 +2544,53 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>740300</v>
+      </c>
+      <c r="E42" s="3">
         <v>644500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>641200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>748300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>704300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>713100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>621700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>641200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>555600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>519400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>47300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>50000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>100000</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2516,53 +2606,56 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>197600</v>
+      </c>
+      <c r="E43" s="3">
         <v>165000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>135200</v>
       </c>
-      <c r="F43" s="3">
-        <v>170900</v>
-      </c>
       <c r="G43" s="3">
-        <v>135600</v>
+        <v>181300</v>
       </c>
       <c r="H43" s="3">
-        <v>105800</v>
+        <v>143000</v>
       </c>
       <c r="I43" s="3">
-        <v>127700</v>
+        <v>111200</v>
       </c>
       <c r="J43" s="3">
+        <v>130800</v>
+      </c>
+      <c r="K43" s="3">
         <v>131100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>93000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>71300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>80400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>57000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46900</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2575,31 +2668,34 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2634,53 +2730,56 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>66300</v>
+        <v>34500</v>
       </c>
       <c r="E45" s="3">
-        <v>66400</v>
+        <v>33800</v>
       </c>
       <c r="F45" s="3">
-        <v>73700</v>
+        <v>31000</v>
       </c>
       <c r="G45" s="3">
-        <v>57100</v>
+        <v>33700</v>
       </c>
       <c r="H45" s="3">
-        <v>51100</v>
+        <v>28700</v>
       </c>
       <c r="I45" s="3">
-        <v>49900</v>
+        <v>29000</v>
       </c>
       <c r="J45" s="3">
+        <v>27500</v>
+      </c>
+      <c r="K45" s="3">
         <v>50200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27500</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,53 +2792,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1192200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1314400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1263000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1280900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1182300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1143200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1115200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1118000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1069400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1064000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1044200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1051800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1012400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>350700</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2752,8 +2854,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2763,33 +2868,33 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>9600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2805,19 +2910,22 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3400</v>
+        <v>4000</v>
       </c>
       <c r="E48" s="3">
         <v>3400</v>
@@ -2826,32 +2934,32 @@
         <v>3400</v>
       </c>
       <c r="G48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H48" s="3">
         <v>4200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2867,56 +2975,59 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E49" s="3">
         <v>37900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>32700</v>
       </c>
-      <c r="F49" s="3">
-        <v>9900</v>
-      </c>
       <c r="G49" s="3">
-        <v>10400</v>
+        <v>10200</v>
       </c>
       <c r="H49" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="I49" s="3">
-        <v>11500</v>
+        <v>11300</v>
       </c>
       <c r="J49" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K49" s="3">
         <v>12000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,53 +3164,56 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>20600</v>
+        <v>3600</v>
       </c>
       <c r="E52" s="3">
-        <v>22500</v>
+        <v>4900</v>
       </c>
       <c r="F52" s="3">
-        <v>23700</v>
+        <v>4800</v>
       </c>
       <c r="G52" s="3">
-        <v>20300</v>
+        <v>4100</v>
       </c>
       <c r="H52" s="3">
-        <v>19600</v>
+        <v>4900</v>
       </c>
       <c r="I52" s="3">
-        <v>19500</v>
+        <v>4500</v>
       </c>
       <c r="J52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K52" s="3">
         <v>19700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,53 +3288,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1252600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1376300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1321600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1317900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1226900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1189100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1164100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1169200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1120200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1115400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1099000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1091400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1028800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>366400</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,53 +3400,54 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3200</v>
+        <v>2200</v>
       </c>
       <c r="E57" s="3">
         <v>3200</v>
       </c>
       <c r="F57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,8 +3460,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3338,35 +3472,35 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>2900</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3382,59 +3516,62 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>663600</v>
+        <v>383200</v>
       </c>
       <c r="E59" s="3">
-        <v>671300</v>
+        <v>613900</v>
       </c>
       <c r="F59" s="3">
-        <v>660300</v>
+        <v>617600</v>
       </c>
       <c r="G59" s="3">
-        <v>580900</v>
+        <v>605900</v>
       </c>
       <c r="H59" s="3">
-        <v>317000</v>
+        <v>538900</v>
       </c>
       <c r="I59" s="3">
-        <v>308000</v>
+        <v>276700</v>
       </c>
       <c r="J59" s="3">
+        <v>270300</v>
+      </c>
+      <c r="K59" s="3">
         <v>301100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>258200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>241300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>226000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>236600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>173900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>149500</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3447,53 +3584,56 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>464500</v>
+      </c>
+      <c r="E60" s="3">
         <v>666800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>674500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>662100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>585900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>321200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>311100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>306300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>264500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>246700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>234600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>241600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>178900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>151500</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,8 +3646,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3524,13 +3667,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3565,52 +3708,55 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>21400</v>
+        <v>3800</v>
       </c>
       <c r="E62" s="3">
-        <v>32700</v>
+        <v>6700</v>
       </c>
       <c r="F62" s="3">
-        <v>37900</v>
+        <v>17500</v>
       </c>
       <c r="G62" s="3">
-        <v>47800</v>
+        <v>3500</v>
       </c>
       <c r="H62" s="3">
-        <v>36600</v>
+        <v>7600</v>
       </c>
       <c r="I62" s="3">
-        <v>37500</v>
+        <v>9900</v>
       </c>
       <c r="J62" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K62" s="3">
         <v>38200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>41100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>46200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>50600</v>
-      </c>
-      <c r="O62" s="3">
-        <v>40500</v>
       </c>
       <c r="P62" s="3">
         <v>40500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>40500</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,53 +3956,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>733400</v>
+        <v>482400</v>
       </c>
       <c r="E66" s="3">
-        <v>753800</v>
+        <v>688300</v>
       </c>
       <c r="F66" s="3">
-        <v>746700</v>
+        <v>707300</v>
       </c>
       <c r="G66" s="3">
-        <v>680300</v>
+        <v>699900</v>
       </c>
       <c r="H66" s="3">
-        <v>405400</v>
+        <v>633700</v>
       </c>
       <c r="I66" s="3">
-        <v>398600</v>
+        <v>357800</v>
       </c>
       <c r="J66" s="3">
+        <v>348500</v>
+      </c>
+      <c r="K66" s="3">
         <v>398200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>356700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>336900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>316900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>316600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>244400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>217500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4043,11 +4211,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>424900</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,53 +4290,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1162000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1191500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1204500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1149800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1113400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-828200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-778100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-725600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-686900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-638500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-579400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-553300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-507600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-466300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,53 +4538,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>724700</v>
+      </c>
+      <c r="E76" s="3">
         <v>642800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>567800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>571200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>546600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>783700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>765500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>771000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>763600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>778500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>782100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>774900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>784400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-276000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E81" s="3">
         <v>12900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-54600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-36500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-285200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-50100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-52500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-48500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-59000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-45800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-41200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-27900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-120000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-28600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,50 +4817,51 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3100</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H83" s="3">
+        <v>900</v>
+      </c>
+      <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4678,8 +4877,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,50 +5187,53 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-36300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5032,8 +5249,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,52 +5275,53 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E91" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-300</v>
       </c>
       <c r="I91" s="3">
         <v>-300</v>
       </c>
       <c r="J91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5108,14 +5329,17 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,50 +5459,53 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-92800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>89400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>14600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-89400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>24400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-81800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-474700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>46100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5291,8 +5521,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,31 +5547,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,50 +5793,53 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E100" s="3">
         <v>12900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>18000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>11900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>34800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>43700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>658900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5609,8 +5855,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5618,41 +5867,41 @@
         <v>-1200</v>
       </c>
       <c r="E101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G101" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K101" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="O101" s="3">
+        <v>7800</v>
+      </c>
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>4900</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="N101" s="3">
-        <v>7800</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5668,50 +5917,53 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-262000</v>
+      </c>
+      <c r="E102" s="3">
         <v>18300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>132300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-45200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>20500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-76800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-476700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>62500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>548500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5725,6 +5977,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>GTLB</t>
   </si>
@@ -656,289 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E8" s="3">
         <v>196000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>182600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>169200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>163800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>139600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>126900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>122900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>113000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>101000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>87400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>77800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>66800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>58100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>49900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>46100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>42200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E9" s="3">
         <v>22100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9200</v>
-      </c>
-      <c r="P9" s="3">
-        <v>7200</v>
       </c>
       <c r="Q9" s="3">
         <v>7200</v>
       </c>
       <c r="R9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="S9" s="3">
         <v>6400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4600</v>
-      </c>
-      <c r="U9" s="3">
-        <v>3800</v>
       </c>
       <c r="V9" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>188600</v>
+      </c>
+      <c r="E10" s="3">
         <v>173900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>161200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>150400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>147800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>134600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>124900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>113400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>108700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>98400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>88000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>77600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>59600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>50900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>43500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>39900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>37600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>30600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,70 +974,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E12" s="3">
         <v>61400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>60900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>54100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>52400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>49000</v>
       </c>
       <c r="I12" s="3">
         <v>49000</v>
       </c>
       <c r="J12" s="3">
+        <v>49000</v>
+      </c>
+      <c r="K12" s="3">
         <v>48300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>43700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>41100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>39500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>31800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>48700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,35 +1102,38 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9000</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7700</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1121,11 +1141,11 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-17800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1141,41 +1161,44 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="E15" s="3">
+        <v>700</v>
+      </c>
+      <c r="F15" s="3">
         <v>800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>223600</v>
+        <v>225800</v>
       </c>
       <c r="E17" s="3">
+        <v>224700</v>
+      </c>
+      <c r="F17" s="3">
         <v>222800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>220500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>198500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>189900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>193500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>177500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>169200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>169900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>166300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>112500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>118400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>99300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>88000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>76000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>174600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>66600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>61600</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-27600</v>
+        <v>-14400</v>
       </c>
       <c r="E18" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-40200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-51300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-34700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-40300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-53900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-50600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-56900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-65300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-25100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-40600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-32500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-29900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-26100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-128500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-24400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-28900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,115 +1411,119 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>10100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>20000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-19400</v>
+        <v>-7500</v>
       </c>
       <c r="E21" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-38400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-51000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-37600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-39300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-55000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-50000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-40100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-48900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-60200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-23000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-48700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1496,14 +1533,17 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-8800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1528,8 +1568,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1564,132 +1604,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-42200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-29600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-47200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-51400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-41700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-50400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-61600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-49600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-42600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-39800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-118400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-33800</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-39400</v>
+        <v>-11300</v>
       </c>
       <c r="E24" s="3">
         <v>-39400</v>
       </c>
       <c r="F24" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="G24" s="3">
         <v>12700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>256800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E26" s="3">
         <v>28300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-54900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-286400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-51200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-52900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-42100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-50500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-61500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-46800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-40800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-28300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-120000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-28600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E27" s="3">
         <v>29600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-54600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-36500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-285200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-50100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-52500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-48500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-59000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-45800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-40200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-27900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-120000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-28600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2189,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-10100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-20000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E33" s="3">
         <v>29600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-54600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-36500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-285200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-50100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-52500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-38700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-48500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-59000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-40200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-27900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-120000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-28600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E35" s="3">
         <v>29600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-54600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-36500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-285200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-50100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-52500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-38700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-48500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-59000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-40200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-27900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-120000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-28600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,56 +2571,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E41" s="3">
         <v>176600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>438600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>420300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>288000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>285300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>273200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>315900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>295400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>372200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>410800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>887500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>884700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>824700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>276300</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,53 +2634,56 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>764700</v>
+      </c>
+      <c r="E42" s="3">
         <v>740300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>644500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>641200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>748300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>704300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>713100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>621700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>641200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>555600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>519400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>47300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>50000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,56 +2699,59 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>264600</v>
+      </c>
+      <c r="E43" s="3">
         <v>197600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>165000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>181300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>143000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>111200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>130800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>131100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>101500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>93000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>71300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>80400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>57000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>46900</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2671,8 +2764,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2697,8 +2793,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2733,56 +2829,59 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E45" s="3">
         <v>34500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>29000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>50200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27500</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,56 +2894,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1336300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1192200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1314400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1263000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1280900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1182300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1143200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1115200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1118000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1069400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1064000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1044200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1051800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1012400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>350700</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +2959,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2874,30 +2979,30 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>9600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>15600</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2913,22 +3018,25 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E48" s="3">
         <v>4000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>3400</v>
       </c>
       <c r="F48" s="3">
         <v>3400</v>
@@ -2937,32 +3045,32 @@
         <v>3400</v>
       </c>
       <c r="H48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I48" s="3">
         <v>4200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,59 +3086,62 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E49" s="3">
         <v>35700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>32700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>600</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,56 +3284,59 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E52" s="3">
         <v>3600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,56 +3414,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1399300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1252600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1376300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1321600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1317900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1226900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1189100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1164100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1169200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1120200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1115400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1099000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1091400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1028800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>366400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3479,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,56 +3531,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>3200</v>
       </c>
       <c r="F57" s="3">
         <v>3200</v>
       </c>
       <c r="G57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,8 +3594,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3475,35 +3609,35 @@
         <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
         <v>400</v>
       </c>
       <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>2900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3519,62 +3653,65 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>383200</v>
+        <v>442600</v>
       </c>
       <c r="E59" s="3">
+        <v>408400</v>
+      </c>
+      <c r="F59" s="3">
         <v>613900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>617600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>605900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>538900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>276700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>270300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>301100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>258200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>241300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>226000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>236600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>173900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>149500</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,56 +3724,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>541100</v>
+      </c>
+      <c r="E60" s="3">
         <v>464500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>666800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>674500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>662100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>585900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>321200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>311100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>306300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>264500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>246700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>234600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>241600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>178900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>151500</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,8 +3789,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3667,17 +3810,17 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
       </c>
       <c r="J61" s="3">
+        <v>100</v>
+      </c>
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3711,55 +3854,58 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>41100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>46200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>50600</v>
-      </c>
-      <c r="P62" s="3">
-        <v>40500</v>
       </c>
       <c r="Q62" s="3">
         <v>40500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>40500</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,56 +4114,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>574100</v>
+      </c>
+      <c r="E66" s="3">
         <v>482400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>688300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>707300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>699900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>633700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>357800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>348500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>398200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>356700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>336900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>316900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>316600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>244400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>217500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4179,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4214,11 +4382,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>424900</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,56 +4464,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1163700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1162000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1191500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1204500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1149800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1113400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-828200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-778100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-725600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-686900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-638500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-579400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-553300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-507600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-466300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4529,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,56 +4724,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>779800</v>
+      </c>
+      <c r="E76" s="3">
         <v>724700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>642800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>567800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>571200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>546600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>783700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>765500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>771000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>763600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>778500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>782100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>774900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>784400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-276000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4789,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E81" s="3">
         <v>29600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-54600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-36500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-285200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-50100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-52500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-38700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-48500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-59000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-40200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-27900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-120000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-28600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,13 +5016,14 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
@@ -4833,38 +5032,38 @@
         <v>1100</v>
       </c>
       <c r="G83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H83" s="3">
         <v>1000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4880,8 +5079,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,53 +5404,56 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-177000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-36300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5252,8 +5469,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,55 +5496,56 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
       </c>
       <c r="J91" s="3">
         <v>-300</v>
       </c>
       <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3500</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5332,14 +5553,17 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,53 +5689,56 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-92800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>89400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>14600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-89400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>24400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-81800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-474700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>46100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5524,8 +5754,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5574,8 +5808,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,53 +6039,56 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E100" s="3">
         <v>2900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>15000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>18000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>11900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>34800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>43700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>658900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5858,53 +6104,56 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>7800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5920,53 +6169,56 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-262000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>132300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-45200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-76800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-476700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>62500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>548500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5980,6 +6232,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -1111,7 +1111,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
@@ -1176,7 +1176,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2700</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>700</v>
@@ -1263,7 +1263,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>225800</v>
+        <v>230300</v>
       </c>
       <c r="E17" s="3">
         <v>224700</v>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-14400</v>
+        <v>-18900</v>
       </c>
       <c r="E18" s="3">
         <v>-28600</v>
@@ -1418,7 +1418,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4200</v>
+        <v>-3700</v>
       </c>
       <c r="E20" s="3">
         <v>-5000</v>
@@ -1430,7 +1430,7 @@
         <v>600</v>
       </c>
       <c r="H20" s="3">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="I20" s="3">
         <v>200</v>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-7500</v>
+        <v>-14700</v>
       </c>
       <c r="E21" s="3">
         <v>-22900</v>
@@ -1495,7 +1495,7 @@
         <v>-51000</v>
       </c>
       <c r="H21" s="3">
-        <v>-37600</v>
+        <v>-38000</v>
       </c>
       <c r="I21" s="3">
         <v>-39300</v>
@@ -1613,7 +1613,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1100</v>
+        <v>-5300</v>
       </c>
       <c r="E23" s="3">
         <v>-11200</v>
@@ -1625,7 +1625,7 @@
         <v>-42200</v>
       </c>
       <c r="H23" s="3">
-        <v>-35800</v>
+        <v>-36200</v>
       </c>
       <c r="I23" s="3">
         <v>-29600</v>
@@ -1678,7 +1678,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-11300</v>
+        <v>-10500</v>
       </c>
       <c r="E24" s="3">
         <v>-39400</v>
@@ -1690,7 +1690,7 @@
         <v>12700</v>
       </c>
       <c r="H24" s="3">
-        <v>1800</v>
+        <v>2900</v>
       </c>
       <c r="I24" s="3">
         <v>256800</v>
@@ -1808,7 +1808,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>10200</v>
+        <v>5200</v>
       </c>
       <c r="E26" s="3">
         <v>28300</v>
@@ -1820,7 +1820,7 @@
         <v>-54900</v>
       </c>
       <c r="H26" s="3">
-        <v>-37600</v>
+        <v>-39100</v>
       </c>
       <c r="I26" s="3">
         <v>-286400</v>
@@ -1873,7 +1873,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>10800</v>
+        <v>5800</v>
       </c>
       <c r="E27" s="3">
         <v>29600</v>
@@ -1885,7 +1885,7 @@
         <v>-54600</v>
       </c>
       <c r="H27" s="3">
-        <v>-36500</v>
+        <v>-38000</v>
       </c>
       <c r="I27" s="3">
         <v>-285200</v>
@@ -2198,7 +2198,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4200</v>
+        <v>3700</v>
       </c>
       <c r="E32" s="3">
         <v>5000</v>
@@ -2210,7 +2210,7 @@
         <v>-600</v>
       </c>
       <c r="H32" s="3">
-        <v>-3900</v>
+        <v>-4300</v>
       </c>
       <c r="I32" s="3">
         <v>-200</v>
@@ -2263,7 +2263,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>10800</v>
+        <v>5800</v>
       </c>
       <c r="E33" s="3">
         <v>29600</v>
@@ -2275,7 +2275,7 @@
         <v>-54600</v>
       </c>
       <c r="H33" s="3">
-        <v>-36500</v>
+        <v>-38000</v>
       </c>
       <c r="I33" s="3">
         <v>-285200</v>
@@ -2393,7 +2393,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>10800</v>
+        <v>5800</v>
       </c>
       <c r="E35" s="3">
         <v>29600</v>
@@ -2405,7 +2405,7 @@
         <v>-54600</v>
       </c>
       <c r="H35" s="3">
-        <v>-36500</v>
+        <v>-38000</v>
       </c>
       <c r="I35" s="3">
         <v>-285200</v>
@@ -2708,7 +2708,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>264600</v>
+        <v>278500</v>
       </c>
       <c r="E43" s="3">
         <v>197600</v>
@@ -2720,7 +2720,7 @@
         <v>135200</v>
       </c>
       <c r="H43" s="3">
-        <v>181300</v>
+        <v>178500</v>
       </c>
       <c r="I43" s="3">
         <v>143000</v>
@@ -2838,7 +2838,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>39000</v>
+        <v>40500</v>
       </c>
       <c r="E45" s="3">
         <v>34500</v>
@@ -2850,7 +2850,7 @@
         <v>31000</v>
       </c>
       <c r="H45" s="3">
-        <v>33700</v>
+        <v>33600</v>
       </c>
       <c r="I45" s="3">
         <v>28700</v>
@@ -2915,7 +2915,7 @@
         <v>1263000</v>
       </c>
       <c r="H46" s="3">
-        <v>1280900</v>
+        <v>1284500</v>
       </c>
       <c r="I46" s="3">
         <v>1182300</v>
@@ -3098,7 +3098,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>34000</v>
+        <v>34100</v>
       </c>
       <c r="E49" s="3">
         <v>35700</v>
@@ -3293,7 +3293,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="E52" s="3">
         <v>3600</v>
@@ -3435,7 +3435,7 @@
         <v>1321600</v>
       </c>
       <c r="H54" s="3">
-        <v>1317900</v>
+        <v>1321400</v>
       </c>
       <c r="I54" s="3">
         <v>1226900</v>
@@ -3603,7 +3603,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>300</v>
@@ -3668,7 +3668,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>442600</v>
+        <v>462000</v>
       </c>
       <c r="E59" s="3">
         <v>408400</v>
@@ -3680,7 +3680,7 @@
         <v>617600</v>
       </c>
       <c r="H59" s="3">
-        <v>605900</v>
+        <v>614900</v>
       </c>
       <c r="I59" s="3">
         <v>538900</v>
@@ -3733,7 +3733,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>541100</v>
+        <v>545000</v>
       </c>
       <c r="E60" s="3">
         <v>464500</v>
@@ -3745,7 +3745,7 @@
         <v>674500</v>
       </c>
       <c r="H60" s="3">
-        <v>662100</v>
+        <v>677200</v>
       </c>
       <c r="I60" s="3">
         <v>585900</v>
@@ -3798,7 +3798,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -3863,7 +3863,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6600</v>
+        <v>6400</v>
       </c>
       <c r="E62" s="3">
         <v>3800</v>
@@ -4123,7 +4123,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>574100</v>
+        <v>578000</v>
       </c>
       <c r="E66" s="3">
         <v>482400</v>
@@ -4135,7 +4135,7 @@
         <v>707300</v>
       </c>
       <c r="H66" s="3">
-        <v>699900</v>
+        <v>715000</v>
       </c>
       <c r="I66" s="3">
         <v>633700</v>
@@ -4473,7 +4473,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1163700</v>
+        <v>-1167600</v>
       </c>
       <c r="E72" s="3">
         <v>-1162000</v>
@@ -4485,7 +4485,7 @@
         <v>-1204500</v>
       </c>
       <c r="H72" s="3">
-        <v>-1149800</v>
+        <v>-1161300</v>
       </c>
       <c r="I72" s="3">
         <v>-1113400</v>
@@ -4733,7 +4733,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>779800</v>
+        <v>775900</v>
       </c>
       <c r="E76" s="3">
         <v>724700</v>
@@ -4745,7 +4745,7 @@
         <v>567800</v>
       </c>
       <c r="H76" s="3">
-        <v>571200</v>
+        <v>559800</v>
       </c>
       <c r="I76" s="3">
         <v>546600</v>
@@ -4933,7 +4933,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>10800</v>
+        <v>5800</v>
       </c>
       <c r="E81" s="3">
         <v>29600</v>
@@ -4945,7 +4945,7 @@
         <v>-54600</v>
       </c>
       <c r="H81" s="3">
-        <v>-36500</v>
+        <v>-38000</v>
       </c>
       <c r="I81" s="3">
         <v>-285200</v>

--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>GTLB</t>
   </si>
@@ -656,302 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E8" s="3">
         <v>211400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>196000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>182600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>169200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>163800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>139600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>126900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>122900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>113000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>101000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>87400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>77800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>66800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>58100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>49900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>46100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>42200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E9" s="3">
         <v>22900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9200</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>7200</v>
       </c>
       <c r="R9" s="3">
         <v>7200</v>
       </c>
       <c r="S9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="T9" s="3">
         <v>6400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4600</v>
-      </c>
-      <c r="V9" s="3">
-        <v>3800</v>
       </c>
       <c r="W9" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>189500</v>
+      </c>
+      <c r="E10" s="3">
         <v>188600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>173900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>161200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>150400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>147800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>134600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>124900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>113400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>108700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>98400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>88000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>77600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>68600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>59600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>50900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>43500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>39900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>37600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>30600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E12" s="3">
         <v>62900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>61400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>60900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>54100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>52400</v>
-      </c>
-      <c r="I12" s="3">
-        <v>49000</v>
       </c>
       <c r="J12" s="3">
         <v>49000</v>
       </c>
       <c r="K12" s="3">
+        <v>49000</v>
+      </c>
+      <c r="L12" s="3">
         <v>48300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>43700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>41100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>39500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>31800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>48700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,38 +1121,41 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>9000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1144,11 +1163,11 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-17800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1164,44 +1183,47 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1235,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>249100</v>
+      </c>
+      <c r="E17" s="3">
         <v>230300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>224700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>222800</v>
       </c>
-      <c r="G17" s="3">
-        <v>220500</v>
-      </c>
       <c r="H17" s="3">
+        <v>222800</v>
+      </c>
+      <c r="I17" s="3">
         <v>198500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>189900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>193500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>169200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>169900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>166300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>112500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>118400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>99300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>88000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>76000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>174600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>66600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>61600</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-28600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-40200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-51300</v>
-      </c>
       <c r="H18" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-34700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-40300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-53900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-50600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-46300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-56900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-65300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-25100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-32500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-29900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-26100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-128500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-24400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-28900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,121 +1444,125 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
       <c r="H20" s="3">
+        <v>900</v>
+      </c>
+      <c r="I20" s="3">
         <v>4300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>20000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-38400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-51000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-38000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-39300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-55000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-50000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-40100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-48900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-60200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-23000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-48700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-42500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1536,14 +1572,17 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-8800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1571,8 +1610,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1607,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27100</v>
       </c>
-      <c r="G23" s="3">
-        <v>-42200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-42500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-36200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-29600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-47200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-51400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-41700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-50400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-61600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-49600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-42600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-39800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-118400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-28400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-33800</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-10500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-39400</v>
       </c>
       <c r="F24" s="3">
         <v>-39400</v>
       </c>
       <c r="G24" s="3">
-        <v>12700</v>
+        <v>-39400</v>
       </c>
       <c r="H24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I24" s="3">
         <v>2900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>256800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="E26" s="3">
         <v>5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-54900</v>
-      </c>
       <c r="H26" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-39100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-286400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-51200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-52900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-42100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-50500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-61500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-46800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-41700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-40800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-28300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-120000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-28600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E27" s="3">
         <v>5800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12900</v>
       </c>
-      <c r="G27" s="3">
-        <v>-54600</v>
-      </c>
       <c r="H27" s="3">
+        <v>-55200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-38000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-285200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-50100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-52500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-48500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-59000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-41200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-40200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-27900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-120000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-28600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-4300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-20000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E33" s="3">
         <v>5800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12900</v>
       </c>
-      <c r="G33" s="3">
-        <v>-54600</v>
-      </c>
       <c r="H33" s="3">
+        <v>-55200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-38000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-285200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-50100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-52500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-48500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-59000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-41200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-40200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-27900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-120000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-28600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E35" s="3">
         <v>5800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12900</v>
       </c>
-      <c r="G35" s="3">
-        <v>-54600</v>
-      </c>
       <c r="H35" s="3">
+        <v>-55200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-38000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-285200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-50100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-52500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-48500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-59000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-41200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-40200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-27900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-120000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-28600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,59 +2657,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>255700</v>
+      </c>
+      <c r="E41" s="3">
         <v>227600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>176600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>438600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>420300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>288000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>285300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>273200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>315900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>295400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>372200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>410800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>887500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>884700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>824700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>276300</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2637,56 +2723,59 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>849100</v>
+      </c>
+      <c r="E42" s="3">
         <v>764700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>740300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>644500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>641200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>748300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>704300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>713100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>621700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>641200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>555600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>519400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>47300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>50000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>100000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2702,59 +2791,62 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E43" s="3">
         <v>278500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>197600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>165000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>135200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>178500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>143000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>111200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>130800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>131100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>101500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>93000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>71300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>80400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>57000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>46900</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2767,8 +2859,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2796,8 +2891,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2832,59 +2927,62 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E45" s="3">
         <v>40500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>50200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>36700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>30600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27500</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2897,59 +2995,62 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1380800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1336300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1192200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1314400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1263000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1284500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1182300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1143200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1115200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1118000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1069400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1064000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1044200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1051800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1012400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>350700</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,8 +3063,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2982,30 +3086,30 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>9600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15600</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3021,25 +3125,28 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>3400</v>
       </c>
       <c r="G48" s="3">
         <v>3400</v>
@@ -3048,32 +3155,32 @@
         <v>3400</v>
       </c>
       <c r="I48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J48" s="3">
         <v>4200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,62 +3196,65 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E49" s="3">
         <v>34100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>37900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>32700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>600</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,59 +3403,62 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E52" s="3">
         <v>4300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,59 +3539,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1442000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1399300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1252600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1376300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1321600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1321400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1226900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1189100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1164100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1169200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1120200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1115400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1099000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1091400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1028800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>366400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,59 +3661,60 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>3200</v>
       </c>
       <c r="G57" s="3">
         <v>3200</v>
       </c>
       <c r="H57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,13 +3727,16 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>300</v>
@@ -3612,35 +3745,35 @@
         <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
         <v>400</v>
       </c>
       <c r="I58" s="3">
+        <v>400</v>
+      </c>
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>2900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3656,65 +3789,68 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>450700</v>
+      </c>
+      <c r="E59" s="3">
         <v>462000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>408400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>613900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>617600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>614900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>538900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>276700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>270300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>301100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>258200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>241300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>226000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>236600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>173900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>149500</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,59 +3863,62 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>556400</v>
+      </c>
+      <c r="E60" s="3">
         <v>545000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>464500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>666800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>674500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>677200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>585900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>321200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>311100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>306300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>264500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>246700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>234600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>241600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>178900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>151500</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3792,17 +3931,20 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -3813,17 +3955,17 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
       </c>
       <c r="K61" s="3">
+        <v>100</v>
+      </c>
+      <c r="L61" s="3">
         <v>500</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3857,58 +3999,61 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E62" s="3">
         <v>6400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>41100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>46200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>50600</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>40500</v>
       </c>
       <c r="R62" s="3">
         <v>40500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>40500</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -3922,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,59 +4271,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>589400</v>
+      </c>
+      <c r="E66" s="3">
         <v>578000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>482400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>688300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>707300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>715000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>633700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>357800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>348500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>398200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>356700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>336900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>316900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>316600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>244400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>217500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4182,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4385,11 +4552,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>424900</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,59 +4637,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1203500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1167600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1162000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1191500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1204500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1161300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1113400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-828200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-778100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-725600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-686900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-638500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-579400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-553300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-507600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-466300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,59 +4909,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>808300</v>
+      </c>
+      <c r="E76" s="3">
         <v>775900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>724700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>642800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>567800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>559800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>546600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>783700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>765500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>771000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>763600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>778500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>782100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>774900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>784400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-276000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E81" s="3">
         <v>5800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12900</v>
       </c>
-      <c r="G81" s="3">
-        <v>-54600</v>
-      </c>
       <c r="H81" s="3">
+        <v>-55200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-38000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-285200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-50100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-52500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-48500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-59000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-41200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-40200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-27900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-120000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-28600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,16 +5214,17 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1100</v>
       </c>
       <c r="F83" s="3">
         <v>1100</v>
@@ -5035,38 +5233,38 @@
         <v>1100</v>
       </c>
       <c r="H83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5082,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,56 +5620,59 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E89" s="3">
         <v>63200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-177000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>27100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-36300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10100</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5472,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,58 +5716,59 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5556,14 +5776,17 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,56 +5918,59 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-81900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-92800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>89400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-35800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>14600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-89400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>24400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-81800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-474700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>46100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5757,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5811,8 +6044,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,56 +6284,59 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E100" s="3">
         <v>11700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>15000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>11900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>34800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>43700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>658900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6107,56 +6352,59 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>7800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6172,56 +6420,59 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E102" s="3">
         <v>51000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-262000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>132300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-45200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-76800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-38600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-476700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>62500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>548500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6235,6 +6486,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GTLB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>GTLB</t>
   </si>
@@ -656,327 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>260400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>244400</v>
+      </c>
+      <c r="F8" s="3">
         <v>236000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>214500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>211400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>196000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>182600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>169200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>163800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>149700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>139600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>126900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>122900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>113000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>101000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>87400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>77800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>66800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>58100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>49900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>46100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>42200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>34400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>32200</v>
+      </c>
+      <c r="F9" s="3">
         <v>28500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>25000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>22900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>22100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>21400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>18800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>16000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>15100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>14700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>13500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>14600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>13000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>9800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>9200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>7200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>7200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>6400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>6200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>4600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>3800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>225600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>212100</v>
+      </c>
+      <c r="F10" s="3">
         <v>207500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>189500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>188600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>173900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>161200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>150400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>147800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>134600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>124900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>113400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>108700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>98400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>88000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>77600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>68600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>59600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>50900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>43500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>39900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>37600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>30600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1028,87 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>68700</v>
+      </c>
+      <c r="F12" s="3">
         <v>71500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>65400</v>
       </c>
-      <c r="F12" s="3">
-        <v>62900</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>62500</v>
+      </c>
+      <c r="I12" s="3">
         <v>61400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>61300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>54100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>52400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>49000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>49000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>48300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>43700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>41100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>39500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>31800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>28600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>24700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>22600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>21300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>48700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>19000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>19800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,59 +1178,65 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>2500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>500</v>
-      </c>
-      <c r="G14" s="3">
-        <v>100</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>6700</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>9000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>7700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-17800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1209,52 +1249,58 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>900</v>
+      </c>
+      <c r="F15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>600</v>
       </c>
-      <c r="F15" s="3">
-        <v>500</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>400</v>
+      </c>
+      <c r="I15" s="3">
         <v>700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1200</v>
       </c>
       <c r="M15" s="3">
         <v>1100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1286,8 +1332,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1362,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>256700</v>
+      </c>
+      <c r="F17" s="3">
         <v>254300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>249100</v>
       </c>
-      <c r="F17" s="3">
-        <v>230300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>224700</v>
-      </c>
       <c r="H17" s="3">
+        <v>224000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>224800</v>
+      </c>
+      <c r="J17" s="3">
         <v>223600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>222800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>198500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>189900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>193500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>177500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>169200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>169900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>166300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>112500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>118400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>99300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>88000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>76000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>174600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>66600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>63300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>61600</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-18400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-34600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-28600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-41000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-53600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-34700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-40300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-53900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-50600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-46300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-56900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-25100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-40600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-32500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-29900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-26100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-128500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-24400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-28900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,150 +1545,164 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>4500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>6500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-9100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-10100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-9900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>10100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-4000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>20000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-18500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-44000</v>
       </c>
-      <c r="F21" s="3">
-        <v>-14700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-22900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-39000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-53600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-38000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-39300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-55000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-50000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-40100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-48900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-60200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-23000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-48700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-42500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1656,11 +1736,11 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1692,150 +1772,168 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-33700</v>
       </c>
-      <c r="F23" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-11200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="J23" s="3">
         <v>-26900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-42500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-36200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-29600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-47200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-51400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-41700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-50400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-61600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-24100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-49600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-42600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-39800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-27000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-118400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-28400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-33800</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F24" s="3">
         <v>2200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>2500</v>
       </c>
-      <c r="F24" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-39400</v>
-      </c>
       <c r="H24" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I24" s="3">
         <v>-39200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="K24" s="3">
         <v>13000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>256800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +2003,168 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-36300</v>
       </c>
-      <c r="F26" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>28300</v>
-      </c>
       <c r="H26" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>27800</v>
+      </c>
+      <c r="J26" s="3">
         <v>12200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-55500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-39100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-286400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-51200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-52900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-42100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-50500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-61500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-26600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-46800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-41700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-40800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-28300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-120000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-28600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-35900</v>
       </c>
-      <c r="F27" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>29600</v>
-      </c>
       <c r="H27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>29100</v>
+      </c>
+      <c r="J27" s="3">
         <v>12900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-55200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-38000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-285200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-50100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-52500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-38700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-48500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-26100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-45800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-41200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-40200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-27900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-120000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-28600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2234,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2311,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2388,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2465,168 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>5000</v>
-      </c>
       <c r="H32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J32" s="3">
         <v>1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-4500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-6500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>9100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>10100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>9900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-10100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>4000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-35900</v>
       </c>
-      <c r="F33" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G33" s="3">
-        <v>29600</v>
-      </c>
       <c r="H33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>29100</v>
+      </c>
+      <c r="J33" s="3">
         <v>12900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-55200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-38000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-285200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-50100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-52500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-38700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-48500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-26100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-45800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-41200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-40200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-27900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-120000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-28600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2696,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-35900</v>
       </c>
-      <c r="F35" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G35" s="3">
-        <v>29600</v>
-      </c>
       <c r="H35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>29100</v>
+      </c>
+      <c r="J35" s="3">
         <v>12900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-55200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-38000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-285200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-50100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-52500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-38700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-48500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-26100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-45800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-41200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-40200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-27900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-120000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-28600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2888,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,68 +2917,70 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>229600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>224200</v>
+      </c>
+      <c r="F41" s="3">
         <v>261400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>255700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>227600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>176600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>438600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>420300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>288000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>285300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>273200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>315900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>295400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>372200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>410800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>887500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>884700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>824700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>276300</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,65 +2990,71 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1030300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>980100</v>
+      </c>
+      <c r="F42" s="3">
         <v>903800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>849100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>764700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>740300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>644500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>641200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>748300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>704300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>713100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>621700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>641200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>555600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>519400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>47300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>50000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>100000</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2887,68 +3067,74 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>321300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>221100</v>
+      </c>
+      <c r="F43" s="3">
         <v>197800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>201400</v>
       </c>
-      <c r="F43" s="3">
-        <v>278500</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
+        <v>274800</v>
+      </c>
+      <c r="I43" s="3">
         <v>197600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>165000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>135200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>178500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>143000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>111200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>130800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>131100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>101500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>93000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>71300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>80400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>57000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>46900</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,8 +3144,14 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2993,11 +3185,11 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3029,68 +3221,74 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F45" s="3">
         <v>35300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>35500</v>
       </c>
-      <c r="F45" s="3">
-        <v>40500</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>50500</v>
+      </c>
+      <c r="I45" s="3">
         <v>34500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>33800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>31000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>33600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>28700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>29000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>27500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>50200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>40200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>40800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>38100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>36700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>30600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>27500</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,68 +3298,74 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1655800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1506900</v>
+      </c>
+      <c r="F46" s="3">
         <v>1436200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1380800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1336300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1192200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1314400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1263000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1284500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1182300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1143200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1115200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1118000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1069400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1044200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1051800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1012400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>350700</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,8 +3375,14 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3197,33 +3407,33 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>9600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>10600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>11700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>12700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>13600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>14600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>15600</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3236,68 +3446,74 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F48" s="3">
         <v>8000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5200</v>
       </c>
-      <c r="F48" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4000</v>
       </c>
-      <c r="H48" s="3">
-        <v>3400</v>
-      </c>
       <c r="I48" s="3">
-        <v>3400</v>
+        <v>4000</v>
       </c>
       <c r="J48" s="3">
         <v>3400</v>
       </c>
       <c r="K48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="M48" s="3">
         <v>4200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3310,71 +3526,77 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>28700</v>
+      </c>
+      <c r="F49" s="3">
         <v>30400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>31800</v>
       </c>
-      <c r="F49" s="3">
-        <v>34100</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I49" s="3">
         <v>35700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>37900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>32700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>10200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>10700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>11300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>11900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>12000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>12600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>13200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>13800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>14400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>600</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3384,8 +3606,14 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3683,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,68 +3760,74 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F52" s="3">
         <v>4600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>4400</v>
       </c>
-      <c r="F52" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I52" s="3">
         <v>3600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>4900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>4800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>4900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>4500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>19700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>19000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>18200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>20900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>21900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>15900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>15100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,8 +3837,14 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,68 +3914,74 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1722700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1570800</v>
+      </c>
+      <c r="F54" s="3">
         <v>1498200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1442000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1399300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1252600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1376300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1321600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1321400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1226900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1189100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1164100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1169200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1120200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1115400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1099000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1091400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1028800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>366400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,8 +3991,14 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +4024,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,68 +4053,70 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F57" s="3">
         <v>11400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>6200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>4900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +4126,14 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3876,47 +4144,47 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
-        <v>300</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>2900</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3929,74 +4197,80 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>563700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>464800</v>
+      </c>
+      <c r="F59" s="3">
         <v>459500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>450700</v>
       </c>
-      <c r="F59" s="3">
-        <v>462000</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>462300</v>
+      </c>
+      <c r="I59" s="3">
         <v>408400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>613900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>617600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>614900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>538900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>276700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>270300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>301100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>258200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>241300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>226000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>236600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>173900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>149500</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,68 +4280,74 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>652100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>565800</v>
+      </c>
+      <c r="F60" s="3">
         <v>553400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>556400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>545000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>464500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>666800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>674500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>677200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>585900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>321200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>311100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>306300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>264500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>246700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>234600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>241600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>178900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>151500</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4077,47 +4357,53 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>100</v>
       </c>
-      <c r="L61" s="3">
-        <v>100</v>
-      </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4148,68 +4434,74 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F62" s="3">
         <v>7100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>6700</v>
       </c>
-      <c r="F62" s="3">
-        <v>6400</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I62" s="3">
         <v>3800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>6700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>17500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>9900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>8000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>38200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>41100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>38400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>46200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>50600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>40500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>40500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4511,14 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4588,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4665,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,68 +4742,74 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>686500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>602800</v>
+      </c>
+      <c r="F66" s="3">
         <v>586600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>589400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>578000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>482400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>688300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>707300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>715000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>633700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>357800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>348500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>398200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>356700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>336900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>316900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>316600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>244400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>217500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4819,14 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4852,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4925,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +5002,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4726,14 +5062,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>424900</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +5079,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,68 +5156,74 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1223600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1221000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1212700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1203500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1167600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1162000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1191500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1204500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1161300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1113400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-828200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-778100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-725600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-686900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-638500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-579400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-553300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-507600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-466300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4885,8 +5233,14 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5310,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5387,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,68 +5464,74 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>990700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>922700</v>
+      </c>
+      <c r="F76" s="3">
         <v>866600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>808300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>775900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>724700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>642800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>567800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>559800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>546600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>783700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>765500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>771000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>763600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>778500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>782100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>774900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>784400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-276000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5169,8 +5541,14 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5618,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-35900</v>
       </c>
-      <c r="F81" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G81" s="3">
-        <v>29600</v>
-      </c>
       <c r="H81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>29100</v>
+      </c>
+      <c r="J81" s="3">
         <v>12900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-55200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-38000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-285200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-50100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-52500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-38700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-48500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-26100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-45800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-41200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-40200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-27900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-120000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-28600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-34200</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,65 +5810,67 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
+        <v>700</v>
+      </c>
+      <c r="G83" s="3">
         <v>900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1100</v>
       </c>
       <c r="I83" s="3">
         <v>1100</v>
       </c>
       <c r="J83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5485,8 +5883,14 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5960,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +6037,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +6114,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +6191,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,65 +6268,71 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>31400</v>
+      </c>
+      <c r="F89" s="3">
         <v>49400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>106300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>63200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-177000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>11700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>38100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>24900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>27100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-11000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-11700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-28200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-10100</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5911,8 +6345,14 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,31 +6378,33 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-8200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-700</v>
@@ -5971,46 +6413,52 @@
         <v>-300</v>
       </c>
       <c r="M91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-3500</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6528,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,65 +6605,71 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-75800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-56600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-81900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-21900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-92800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-5200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>89400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-35800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>14600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-89400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>24400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-81800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-40400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-474700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-8800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>46100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-100000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6222,8 +6682,14 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6715,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6284,11 +6752,11 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6320,8 +6788,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6865,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6942,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,65 +7019,71 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F100" s="3">
         <v>12400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>11700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>12900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>5100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>15000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>4700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>18000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>7500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>11900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>7100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>34800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>43700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>9600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>658900</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6604,65 +7096,71 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>4900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-3900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-3900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>7800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6675,65 +7173,71 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="F102" s="3">
         <v>5700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>28100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>51000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-262000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>18300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>132300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>12100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-45200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>20500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-76800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-38600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-476700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>62500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>548500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6744,6 +7248,12 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
